--- a/tams-valuation-parent/tams-valuation-lossmodel/src/main/resources/tpl/ModStagePara001.xlsx
+++ b/tams-valuation-parent/tams-valuation-lossmodel/src/main/resources/tpl/ModStagePara001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="2430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="2436"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>资产所属阶段</t>
   </si>
@@ -26,6 +26,10 @@
   </si>
   <si>
     <t>参数值</t>
+  </si>
+  <si>
+    <t>启用状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -402,27 +406,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.26953125" customWidth="1"/>
-    <col min="2" max="2" width="15.7265625" customWidth="1"/>
-    <col min="3" max="3" width="28.81640625" customWidth="1"/>
-    <col min="4" max="4" width="16.6328125" customWidth="1"/>
+    <col min="1" max="1" width="16.21875" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
     <col min="5" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="17.453125" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="19.7265625" customWidth="1"/>
-    <col min="10" max="10" width="20.26953125" customWidth="1"/>
-    <col min="11" max="11" width="18.7265625" customWidth="1"/>
-    <col min="12" max="12" width="18.26953125" customWidth="1"/>
-    <col min="13" max="13" width="16.90625" customWidth="1"/>
-    <col min="14" max="14" width="15.6328125" customWidth="1"/>
-    <col min="15" max="15" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.77734375" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" customWidth="1"/>
+    <col min="11" max="11" width="18.77734375" customWidth="1"/>
+    <col min="12" max="12" width="18.21875" customWidth="1"/>
+    <col min="13" max="13" width="16.88671875" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" customWidth="1"/>
+    <col min="15" max="15" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,6 +439,9 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
